--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26541,13 +26541,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="O141" t="n">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="R141" t="n">
-        <v>1.015496240067032</v>
+        <v>1.029062029533576</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26686,13 +26686,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="O142" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="R142" t="n">
-        <v>0.06201503756134547</v>
+        <v>0.1162781954275228</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28371</v>
+        <v>28406</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26541,13 +26541,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="O141" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R141" t="n">
-        <v>1.029062029533576</v>
+        <v>1.036813909228745</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26686,13 +26686,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="O142" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1162781954275228</v>
+        <v>0.1724793232174921</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28406</v>
+        <v>28439</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26541,13 +26541,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O141" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="R141" t="n">
-        <v>1.036813909228745</v>
+        <v>1.040689849076329</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26686,13 +26686,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="O142" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1724793232174921</v>
+        <v>0.1860451126840364</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28439</v>
+        <v>28448</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26502,12 +26502,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -26541,13 +26541,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>537</v>
+        <v>1032</v>
       </c>
       <c r="O141" t="n">
-        <v>537</v>
+        <v>1032</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.040689849076329</v>
+        <v>0.07304053433960787</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26580,42 +26583,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -26677,22 +26680,22 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>96</v>
+        <v>537</v>
       </c>
       <c r="O142" t="n">
-        <v>96</v>
+        <v>537</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1860451126840364</v>
+        <v>1.040689849076329</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26759,6 +26762,151 @@
         </is>
       </c>
       <c r="BC142" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>96</v>
+      </c>
+      <c r="O143" t="n">
+        <v>96</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.1860451126840364</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -26880,7 +27028,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -26890,7 +27038,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -26942,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28448</v>
+        <v>29480</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26689,13 +26689,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O142" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="R142" t="n">
-        <v>1.040689849076329</v>
+        <v>1.042627819000121</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26834,13 +26834,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="O143" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1860451126840364</v>
+        <v>0.2693778194070944</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29480</v>
+        <v>29524</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26834,13 +26834,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="O143" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="R143" t="n">
-        <v>0.2693778194070944</v>
+        <v>0.339144736663608</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29524</v>
+        <v>29560</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26689,13 +26689,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O142" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="R142" t="n">
-        <v>1.042627819000121</v>
+        <v>1.044565788923913</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26834,13 +26834,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="O143" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="R143" t="n">
-        <v>0.339144736663608</v>
+        <v>0.3527105261301524</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29560</v>
+        <v>29568</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26689,13 +26689,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O142" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R142" t="n">
-        <v>1.044565788923913</v>
+        <v>1.046503758847705</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26834,13 +26834,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="O143" t="n">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="R143" t="n">
-        <v>0.3527105261301524</v>
+        <v>0.4767406012528433</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29568</v>
+        <v>29633</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -26689,13 +26689,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="O142" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R142" t="n">
-        <v>1.046503758847705</v>
+        <v>1.052317668619081</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26834,13 +26834,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>246</v>
+        <v>297</v>
       </c>
       <c r="O143" t="n">
-        <v>246</v>
+        <v>297</v>
       </c>
       <c r="R143" t="n">
-        <v>0.4767406012528433</v>
+        <v>0.5755770673662376</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29633</v>
+        <v>29687</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -19215,13 +19215,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O101" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R101" t="n">
-        <v>1.043558115751466</v>
+        <v>1.030005412949499</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -26650,12 +26650,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -26689,13 +26689,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>543</v>
+        <v>27</v>
       </c>
       <c r="O142" t="n">
-        <v>543</v>
+        <v>27</v>
       </c>
       <c r="R142" t="n">
-        <v>1.052317668619081</v>
+        <v>0.3659229756531115</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26728,42 +26728,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26825,22 +26825,22 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>297</v>
+        <v>543</v>
       </c>
       <c r="O143" t="n">
-        <v>297</v>
+        <v>543</v>
       </c>
       <c r="R143" t="n">
-        <v>0.5755770673662376</v>
+        <v>1.052317668619081</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -26907,6 +26907,151 @@
         </is>
       </c>
       <c r="BC143" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>388</v>
+      </c>
+      <c r="O144" t="n">
+        <v>388</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.7519323304313138</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -27028,7 +27173,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -27038,7 +27183,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -27090,7 +27235,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29687</v>
+        <v>29804</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -23902,12 +23902,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -23941,10 +23941,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="O127" t="n">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
@@ -24053,12 +24053,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -24092,10 +24092,10 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="O128" t="n">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -24250,7 +24250,7 @@
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
@@ -24287,12 +24287,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -24326,10 +24326,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="O129" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
@@ -24438,12 +24438,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -24477,10 +24477,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="O130" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -24711,10 +24711,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="O131" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
@@ -24823,12 +24823,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -24862,10 +24862,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="O132" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
@@ -25057,12 +25057,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -25096,10 +25096,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O133" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
@@ -25208,12 +25208,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -25247,10 +25247,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O134" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
@@ -25442,12 +25442,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="O135" t="n">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
@@ -25593,12 +25593,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -25632,10 +25632,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="O136" t="n">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -25790,7 +25790,7 @@
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
@@ -25827,12 +25827,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -25866,10 +25866,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="O137" t="n">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
@@ -25978,12 +25978,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -26017,10 +26017,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="O138" t="n">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
@@ -26212,12 +26212,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -26251,81 +26251,87 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="O139" t="n">
-        <v>62</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.8402675737219598</v>
+        <v>12</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -26352,17 +26358,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -26396,81 +26402,170 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>852</v>
+        <v>12</v>
       </c>
       <c r="O140" t="n">
-        <v>852</v>
-      </c>
-      <c r="R140" t="n">
-        <v>1.651150375070823</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -26502,12 +26597,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -26532,25 +26627,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1032</v>
+        <v>62</v>
       </c>
       <c r="O141" t="n">
-        <v>1032</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R141" t="n">
-        <v>0.07304053433960787</v>
+        <v>0.8402675737219598</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26583,42 +26675,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26650,12 +26742,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -26680,22 +26772,22 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>27</v>
+        <v>852</v>
       </c>
       <c r="O142" t="n">
-        <v>27</v>
+        <v>852</v>
       </c>
       <c r="R142" t="n">
-        <v>0.3659229756531115</v>
+        <v>1.651150375070823</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26728,42 +26820,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26795,12 +26887,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26834,13 +26926,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>543</v>
+        <v>1032</v>
       </c>
       <c r="O143" t="n">
-        <v>543</v>
+        <v>1032</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.052317668619081</v>
+        <v>0.07304053433960787</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -26873,42 +26968,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -26940,118 +27035,3103 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>30</v>
+      </c>
+      <c r="O144" t="n">
+        <v>30</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>30</v>
+      </c>
+      <c r="O145" t="n">
+        <v>30</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>153</v>
+      </c>
+      <c r="O146" t="n">
+        <v>153</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>153</v>
+      </c>
+      <c r="O147" t="n">
+        <v>153</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>69</v>
+      </c>
+      <c r="O148" t="n">
+        <v>69</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>69</v>
+      </c>
+      <c r="O149" t="n">
+        <v>69</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>34</v>
+      </c>
+      <c r="O150" t="n">
+        <v>34</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>34</v>
+      </c>
+      <c r="O151" t="n">
+        <v>34</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>26</v>
+      </c>
+      <c r="O152" t="n">
+        <v>26</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>26</v>
+      </c>
+      <c r="O153" t="n">
+        <v>26</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>71</v>
+      </c>
+      <c r="O154" t="n">
+        <v>71</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>71</v>
+      </c>
+      <c r="O155" t="n">
+        <v>71</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>9</v>
+      </c>
+      <c r="O156" t="n">
+        <v>9</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>9</v>
+      </c>
+      <c r="O157" t="n">
+        <v>9</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SCARLET_FEVER; SER_CN_PROV_REPORT_SCARLET_FEVER</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>27</v>
+      </c>
+      <c r="O158" t="n">
+        <v>27</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.3659229756531115</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
         <is>
           <t>猩红热</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>543</v>
+      </c>
+      <c r="O159" t="n">
+        <v>543</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1.052317668619081</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N144" t="n">
+      <c r="N160" t="n">
         <v>388</v>
       </c>
-      <c r="O144" t="n">
+      <c r="O160" t="n">
         <v>388</v>
       </c>
-      <c r="R144" t="n">
+      <c r="R160" t="n">
         <v>0.7519323304313138</v>
       </c>
-      <c r="S144" t="inlineStr">
+      <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO144" t="inlineStr">
+      <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP144" t="inlineStr">
+      <c r="AP160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR144" t="inlineStr">
+      <c r="AR160" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS144" t="inlineStr"/>
-      <c r="AT144" t="n">
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
         <v>0</v>
       </c>
-      <c r="AU144" t="inlineStr">
+      <c r="AU160" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV144" t="inlineStr">
+      <c r="AV160" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW144" t="inlineStr">
+      <c r="AW160" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
+      <c r="AX160" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY144" t="inlineStr">
+      <c r="AY160" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
+      <c r="AZ160" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA144" t="inlineStr">
+      <c r="BA160" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB144" t="inlineStr">
+      <c r="BB160" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC144" t="inlineStr">
+      <c r="BC160" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -27173,7 +30253,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -27183,7 +30263,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -27203,7 +30283,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -27235,7 +30315,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29804</v>
+        <v>30235</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -29914,13 +29914,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O159" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R159" t="n">
-        <v>1.052317668619081</v>
+        <v>1.054255638542873</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -30059,13 +30059,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="O160" t="n">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="R160" t="n">
-        <v>0.7519323304313138</v>
+        <v>0.9341015032677661</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -30132,6 +30132,151 @@
         </is>
       </c>
       <c r="BC160" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>24</v>
+      </c>
+      <c r="O161" t="n">
+        <v>24</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.0465112781710091</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -30170,7 +30315,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -30253,7 +30398,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -30263,7 +30408,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -30315,7 +30460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30235</v>
+        <v>30354</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -30059,13 +30059,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="O160" t="n">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="R160" t="n">
-        <v>0.9341015032677661</v>
+        <v>0.9612330822008548</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -30204,13 +30204,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="O161" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="R161" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.1337199247416512</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30354</v>
+        <v>30413</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -30059,13 +30059,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="O160" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="R160" t="n">
-        <v>0.9612330822008548</v>
+        <v>0.9709229318198149</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -30204,13 +30204,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="O161" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="R161" t="n">
-        <v>0.1337199247416512</v>
+        <v>0.1627894735985319</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30413</v>
+        <v>30433</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4386,6 +4391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4531,6 +4541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4679,6 +4694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8289,6 +8309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8434,6 +8459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8582,6 +8612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11807,6 +11842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11952,6 +11992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12100,6 +12145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15325,6 +15375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15470,6 +15525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15618,6 +15678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19228,6 +19293,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19373,6 +19443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19521,6 +19596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22746,6 +22826,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22891,6 +22976,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23039,6 +23129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26649,6 +26744,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26794,6 +26894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26942,6 +27047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29782,6 +29892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29927,6 +30042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30059,17 +30179,22 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="O160" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="R160" t="n">
-        <v>0.9709229318198149</v>
+        <v>0.9786748115149831</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -30204,17 +30329,22 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="O161" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="R161" t="n">
-        <v>0.1627894735985319</v>
+        <v>0.1918590224554125</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -30460,7 +30590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30433</v>
+        <v>30452</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -30179,13 +30179,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="O160" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="R160" t="n">
-        <v>0.9786748115149831</v>
+        <v>0.9903026310577355</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -30329,13 +30329,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="O161" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="R161" t="n">
-        <v>0.1918590224554125</v>
+        <v>0.2499981201691739</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30452</v>
+        <v>30488</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -30179,13 +30179,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="O160" t="n">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="R160" t="n">
-        <v>0.9903026310577355</v>
+        <v>1.005806390448072</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -30329,13 +30329,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="O161" t="n">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="R161" t="n">
-        <v>0.2499981201691739</v>
+        <v>0.4282913531580421</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30488</v>
+        <v>30588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27874,13 +27874,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R195" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31429</v>
+        <v>31430</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="O191" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="R191" t="n">
-        <v>0.6976691725651365</v>
+        <v>0.8042575183736991</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31430</v>
+        <v>31485</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="O191" t="n">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8042575183736991</v>
+        <v>0.8372030070781639</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31485</v>
+        <v>31502</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O191" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8372030070781639</v>
+        <v>0.8430169168495401</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31502</v>
+        <v>31505</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -28233,6 +28233,150 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>7</v>
+      </c>
+      <c r="O198" t="n">
+        <v>7</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.008368775295968314</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28266,7 +28410,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -28349,7 +28493,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -28359,7 +28503,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
@@ -28411,7 +28555,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31505</v>
+        <v>31512</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>435</v>
+        <v>541</v>
       </c>
       <c r="O191" t="n">
-        <v>435</v>
+        <v>541</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8430169168495401</v>
+        <v>1.048441728771497</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31512</v>
+        <v>31618</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="O191" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="R191" t="n">
-        <v>1.048441728771497</v>
+        <v>1.073635337780793</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31618</v>
+        <v>31631</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d031/2026-2029.xlsx
+++ b/diseases/d031/2026-2029.xlsx
@@ -2175,6 +2175,11 @@
       <c r="R12" t="n">
         <v>1.124874332563269</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2187,13 +2192,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2310,6 +2325,11 @@
       <c r="R13" t="n">
         <v>2.352695487483544</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2322,13 +2342,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7920,6 +7950,11 @@
       <c r="R44" t="n">
         <v>0.7453986541081902</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7932,13 +7967,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8055,6 +8100,11 @@
       <c r="R45" t="n">
         <v>1.647274435223239</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8067,13 +8117,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -13914,6 +13974,11 @@
       <c r="R77" t="n">
         <v>1.084216224157367</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13926,13 +13991,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14049,6 +14124,11 @@
       <c r="R78" t="n">
         <v>1.992233081658223</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14061,13 +14141,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -20286,6 +20376,11 @@
       <c r="R112" t="n">
         <v>0.8538202765239269</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20298,13 +20393,23 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -20421,6 +20526,11 @@
       <c r="R113" t="n">
         <v>2.300370299541159</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20433,13 +20543,23 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -25674,6 +25794,11 @@
       <c r="R143" t="n">
         <v>1.030005412949499</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25686,13 +25811,23 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25809,6 +25944,11 @@
       <c r="R144" t="n">
         <v>2.732537592546785</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25821,13 +25961,23 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
       </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV144" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -33030,6 +33180,11 @@
       <c r="R183" t="n">
         <v>1.097768926959335</v>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33042,13 +33197,23 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
       </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV183" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33165,6 +33330,11 @@
       <c r="R184" t="n">
         <v>2.333315788245623</v>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33177,13 +33347,23 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
       </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV184" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -39354,6 +39534,11 @@
       <c r="R218" t="n">
         <v>0.8402675737219598</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39366,13 +39551,23 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
       </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV218" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39489,6 +39684,11 @@
       <c r="R219" t="n">
         <v>1.651150375070823</v>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39501,13 +39701,23 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
       </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV219" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -46179,6 +46389,11 @@
       <c r="R255" t="n">
         <v>0.3659229756531115</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46191,13 +46406,23 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
       </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV255" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46314,6 +46539,11 @@
       <c r="R256" t="n">
         <v>1.054255638542873</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46326,13 +46556,23 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
       </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV256" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -53707,12 +53947,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -53746,13 +53986,18 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>522</v>
+        <v>46</v>
       </c>
       <c r="O294" t="n">
-        <v>522</v>
+        <v>46</v>
       </c>
       <c r="R294" t="n">
-        <v>1.011620300219448</v>
+        <v>0.6234243288904863</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
@@ -53766,51 +54011,61 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr"/>
       <c r="AT294" t="n">
         <v>0</v>
       </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV294" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -53842,12 +54097,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -53872,7 +54127,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -53881,95 +54136,86 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>9</v>
+        <v>522</v>
       </c>
       <c r="O295" t="n">
-        <v>9</v>
+        <v>522</v>
       </c>
       <c r="R295" t="n">
-        <v>0.01075985395195926</v>
+        <v>1.011620300219448</v>
       </c>
       <c r="S295" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ295" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS295" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr"/>
       <c r="AT295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -53996,7 +54242,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -54045,98 +54291,23 @@
       <c r="O296" t="n">
         <v>9</v>
       </c>
+      <c r="R296" t="n">
+        <v>0.01075985395195926</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U296" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W296" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X296" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y296" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD296" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE296" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF296" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG296" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ296" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL296" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM296" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN296" t="b">
-        <v>1</v>
       </c>
       <c r="AO296" t="inlineStr">
         <is>
@@ -54326,7 +54497,7 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
-          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE297" t="inlineStr">
@@ -54464,17 +54635,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -54508,49 +54679,127 @@
         </is>
       </c>
       <c r="N298" t="n">
+        <v>9</v>
+      </c>
+      <c r="O298" t="n">
+        <v>9</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL298" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN298" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AT298" t="n">
         <v>3</v>
       </c>
-      <c r="O298" t="n">
-        <v>3</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
-      <c r="AA298" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO298" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP298" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
-      <c r="AT298" t="n">
-        <v>1</v>
-      </c>
       <c r="AU298" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
@@ -54568,12 +54817,12 @@
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
@@ -54588,12 +54837,12 @@
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -54620,7 +54869,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -54669,98 +54918,20 @@
       <c r="O299" t="n">
         <v>3</v>
       </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U299" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE299" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM299" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN299" t="b">
-        <v>1</v>
       </c>
       <c r="AO299" t="inlineStr">
         <is>
@@ -54854,17 +55025,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -54898,25 +55069,103 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O300" t="n">
-        <v>6</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA300" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN300" t="b">
+        <v>1</v>
       </c>
       <c r="AO300" t="inlineStr">
         <is>
@@ -55010,7 +55259,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -55059,98 +55308,20 @@
       <c r="O301" t="n">
         <v>6</v>
       </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U301" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y301" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE301" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ301" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL301" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM301" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN301" t="b">
-        <v>1</v>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
@@ -55244,17 +55415,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -55279,7 +55450,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -55288,29 +55459,104 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O302" t="n">
-        <v>8</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.009564314623963786</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U302" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL302" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN302" t="b">
+        <v>1</v>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -55332,7 +55578,7 @@
         </is>
       </c>
       <c r="AT302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
@@ -55351,12 +55597,12 @@
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
@@ -55371,12 +55617,12 @@
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55403,7 +55649,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -55452,98 +55698,23 @@
       <c r="O303" t="n">
         <v>8</v>
       </c>
+      <c r="R303" t="n">
+        <v>0.009564314623963786</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U303" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X303" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y303" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC303" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD303" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE303" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF303" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG303" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH303" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI303" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ303" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL303" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM303" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN303" t="b">
-        <v>1</v>
       </c>
       <c r="AO303" t="inlineStr">
         <is>
@@ -55733,7 +55904,7 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
-          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE304" t="inlineStr">
@@ -55871,17 +56042,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -55915,49 +56086,127 @@
         </is>
       </c>
       <c r="N305" t="n">
+        <v>8</v>
+      </c>
+      <c r="O305" t="n">
+        <v>8</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL305" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP305" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AT305" t="n">
         <v>3</v>
       </c>
-      <c r="O305" t="n">
-        <v>3</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
-      <c r="AA305" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO305" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP305" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ305" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS305" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
-      <c r="AT305" t="n">
-        <v>1</v>
-      </c>
       <c r="AU305" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
@@ -55975,12 +56224,12 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
@@ -55995,12 +56244,12 @@
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -56027,7 +56276,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -56076,98 +56325,20 @@
       <c r="O306" t="n">
         <v>3</v>
       </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U306" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X306" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y306" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA306" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB306" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC306" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE306" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF306" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG306" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ306" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL306" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM306" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN306" t="b">
-        <v>1</v>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
@@ -56261,17 +56432,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -56305,25 +56476,103 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O307" t="n">
-        <v>5</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U307" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL307" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM307" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN307" t="b">
+        <v>1</v>
       </c>
       <c r="AO307" t="inlineStr">
         <is>
@@ -56417,7 +56666,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -56466,98 +56715,20 @@
       <c r="O308" t="n">
         <v>5</v>
       </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U308" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y308" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE308" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG308" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ308" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL308" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM308" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN308" t="b">
-        <v>1</v>
       </c>
       <c r="AO308" t="inlineStr">
         <is>
@@ -56651,17 +56822,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -56686,7 +56857,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -56695,29 +56866,104 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O309" t="n">
-        <v>8</v>
-      </c>
-      <c r="R309" t="n">
-        <v>0.009564314623963786</v>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U309" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL309" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -56739,7 +56985,7 @@
         </is>
       </c>
       <c r="AT309" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
@@ -56758,12 +57004,12 @@
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
@@ -56778,12 +57024,12 @@
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56810,7 +57056,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -56859,98 +57105,23 @@
       <c r="O310" t="n">
         <v>8</v>
       </c>
+      <c r="R310" t="n">
+        <v>0.009564314623963786</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U310" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X310" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y310" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD310" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE310" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF310" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG310" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ310" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL310" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM310" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN310" t="b">
-        <v>1</v>
       </c>
       <c r="AO310" t="inlineStr">
         <is>
@@ -57140,7 +57311,7 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
-          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE311" t="inlineStr">
@@ -57278,17 +57449,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -57322,26 +57493,104 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O312" t="n">
-        <v>6</v>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA312" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM312" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN312" t="b">
+        <v>1</v>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -57363,7 +57612,7 @@
         </is>
       </c>
       <c r="AT312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
@@ -57382,12 +57631,12 @@
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
@@ -57402,12 +57651,12 @@
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -57434,7 +57683,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -57483,98 +57732,20 @@
       <c r="O313" t="n">
         <v>6</v>
       </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U313" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W313" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X313" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA313" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD313" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE313" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG313" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL313" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM313" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN313" t="b">
-        <v>1</v>
       </c>
       <c r="AO313" t="inlineStr">
         <is>
@@ -57668,17 +57839,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -57712,25 +57883,103 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O314" t="n">
-        <v>2</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN314" t="b">
+        <v>1</v>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
@@ -57824,7 +58073,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -57873,98 +58122,20 @@
       <c r="O315" t="n">
         <v>2</v>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U315" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN315" t="b">
-        <v>1</v>
       </c>
       <c r="AO315" t="inlineStr">
         <is>
@@ -58058,17 +58229,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -58093,7 +58264,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -58102,29 +58273,104 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O316" t="n">
-        <v>4</v>
-      </c>
-      <c r="R316" t="n">
-        <v>0.004782157311981893</v>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN316" t="b">
+        <v>1</v>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -58146,7 +58392,7 @@
         </is>
       </c>
       <c r="AT316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
@@ -58165,12 +58411,12 @@
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
@@ -58185,12 +58431,12 @@
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58217,7 +58463,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -58266,98 +58512,23 @@
       <c r="O317" t="n">
         <v>4</v>
       </c>
+      <c r="R317" t="n">
+        <v>0.004782157311981893</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U317" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL317" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN317" t="b">
-        <v>1</v>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
@@ -58547,7 +58718,7 @@
       </c>
       <c r="AD318" t="inlineStr">
         <is>
-          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE318" t="inlineStr">
@@ -58685,17 +58856,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -58729,48 +58900,126 @@
         </is>
       </c>
       <c r="N319" t="n">
+        <v>4</v>
+      </c>
+      <c r="O319" t="n">
+        <v>4</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
         <v>1</v>
       </c>
-      <c r="O319" t="n">
-        <v>1</v>
-      </c>
-      <c r="S319" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO319" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP319" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ319" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS319" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
       <c r="AT319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU319" t="inlineStr">
         <is>
@@ -58789,12 +59038,12 @@
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ319" t="inlineStr">
@@ -58809,12 +59058,12 @@
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -58841,7 +59090,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -58890,98 +59139,20 @@
       <c r="O320" t="n">
         <v>1</v>
       </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U320" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X320" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA320" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG320" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI320" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ320" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL320" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM320" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN320" t="b">
-        <v>1</v>
       </c>
       <c r="AO320" t="inlineStr">
         <is>
@@ -59075,17 +59246,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -59119,25 +59290,103 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O321" t="n">
-        <v>3</v>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>1</v>
       </c>
       <c r="AO321" t="inlineStr">
         <is>
@@ -59231,7 +59480,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -59280,98 +59529,20 @@
       <c r="O322" t="n">
         <v>3</v>
       </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U322" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL322" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM322" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN322" t="b">
-        <v>1</v>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
@@ -59465,17 +59636,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -59500,80 +59671,179 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N323" t="n">
-        <v>554</v>
+        <v>3</v>
       </c>
       <c r="O323" t="n">
-        <v>554</v>
-      </c>
-      <c r="R323" t="n">
-        <v>1.073635337780793</v>
+        <v>3</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL323" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN323" t="b">
+        <v>1</v>
       </c>
       <c r="AO323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS323" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
       <c r="AT323" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59605,12 +59875,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -59635,7 +59905,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -59644,95 +59914,86 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="O324" t="n">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="R324" t="n">
-        <v>0.01434647193594568</v>
+        <v>1.145340224961099</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO324" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ324" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS324" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr"/>
       <c r="AT324" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -59759,7 +60020,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -59808,98 +60069,23 @@
       <c r="O325" t="n">
         <v>12</v>
       </c>
+      <c r="R325" t="n">
+        <v>0.01434647193594568</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U325" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X325" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA325" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ325" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL325" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM325" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN325" t="b">
-        <v>1</v>
       </c>
       <c r="AO325" t="inlineStr">
         <is>
@@ -60089,7 +60275,7 @@
       </c>
       <c r="AD326" t="inlineStr">
         <is>
-          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE326" t="inlineStr">
@@ -60227,17 +60413,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -60271,26 +60457,104 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O327" t="n">
-        <v>6</v>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA327" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>sha256:01fbf7eeba6588d1183c1cd5190dbe79a4ca2189caf0bd3e6e210267eb20db81</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL327" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
+        <v>1</v>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -60312,7 +60576,7 @@
         </is>
       </c>
       <c r="AT327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
@@ -60331,12 +60595,12 @@
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
@@ -60351,12 +60615,12 @@
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -60383,7 +60647,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -60432,98 +60696,20 @@
       <c r="O328" t="n">
         <v>6</v>
       </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U328" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W328" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X328" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y328" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC328" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD328" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE328" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF328" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG328" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI328" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ328" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL328" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM328" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN328" t="b">
-        <v>1</v>
       </c>
       <c r="AO328" t="inlineStr">
         <is>
@@ -60617,17 +60803,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -60666,20 +60852,98 @@
       <c r="O329" t="n">
         <v>6</v>
       </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U329" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL329" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN329" t="b">
+        <v>1</v>
       </c>
       <c r="AO329" t="inlineStr">
         <is>
@@ -60773,7 +61037,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -60822,98 +61086,20 @@
       <c r="O330" t="n">
         <v>6</v>
       </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U330" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W330" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X330" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y330" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA330" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE330" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI330" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ330" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL330" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM330" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN330" t="b">
-        <v>1</v>
       </c>
       <c r="AO330" t="inlineStr">
         <is>
@@ -61007,17 +61193,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -61042,7 +61228,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -61051,29 +61237,104 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O331" t="n">
-        <v>4</v>
-      </c>
-      <c r="R331" t="n">
-        <v>0.004782157311981893</v>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U331" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA331" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL331" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN331" t="b">
+        <v>1</v>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -61095,7 +61356,7 @@
         </is>
       </c>
       <c r="AT331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU331" t="inlineStr">
         <is>
@@ -61114,12 +61375,12 @@
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
@@ -61134,12 +61395,12 @@
       </c>
       <c r="BB331" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC331" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61166,7 +61427,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -61215,98 +61476,23 @@
       <c r="O332" t="n">
         <v>4</v>
       </c>
+      <c r="R332" t="n">
+        <v>0.004782157311981893</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U332" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W332" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X332" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD332" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE332" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI332" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ332" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL332" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM332" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN332" t="b">
-        <v>1</v>
       </c>
       <c r="AO332" t="inlineStr">
         <is>
@@ -61400,17 +61586,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -61444,48 +61630,126 @@
         </is>
       </c>
       <c r="N333" t="n">
+        <v>4</v>
+      </c>
+      <c r="O333" t="n">
+        <v>4</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL333" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN333" t="b">
         <v>1</v>
       </c>
-      <c r="O333" t="n">
-        <v>1</v>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="AA333" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO333" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP333" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ333" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS333" t="inlineStr">
-        <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
-        </is>
-      </c>
       <c r="AT333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
@@ -61504,12 +61768,12 @@
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ333" t="inlineStr">
@@ -61524,12 +61788,12 @@
       </c>
       <c r="BB333" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC333" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -61556,7 +61820,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -61605,98 +61869,20 @@
       <c r="O334" t="n">
         <v>1</v>
       </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U334" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA334" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL334" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM334" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN334" t="b">
-        <v>1</v>
       </c>
       <c r="AO334" t="inlineStr">
         <is>
@@ -61790,17 +61976,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-ST</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Sachsen-Anhalt, Germany</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -61839,20 +62025,98 @@
       <c r="O335" t="n">
         <v>1</v>
       </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U335" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL335" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN335" t="b">
+        <v>1</v>
       </c>
       <c r="AO335" t="inlineStr">
         <is>
@@ -61946,7 +62210,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -61995,98 +62259,20 @@
       <c r="O336" t="n">
         <v>1</v>
       </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U336" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W336" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X336" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y336" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA336" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB336" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD336" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE336" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF336" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ336" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL336" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM336" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN336" t="b">
-        <v>1</v>
       </c>
       <c r="AO336" t="inlineStr">
         <is>
@@ -62180,17 +62366,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -62215,7 +62401,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -62224,29 +62410,104 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O337" t="n">
-        <v>7</v>
-      </c>
-      <c r="R337" t="n">
-        <v>0.008368775295968314</v>
-      </c>
-      <c r="S337" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U337" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA337" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL337" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN337" t="b">
+        <v>1</v>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -62268,7 +62529,7 @@
         </is>
       </c>
       <c r="AT337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU337" t="inlineStr">
         <is>
@@ -62287,12 +62548,12 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ337" t="inlineStr">
@@ -62307,12 +62568,12 @@
       </c>
       <c r="BB337" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC337" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -62339,7 +62600,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -62388,98 +62649,23 @@
       <c r="O338" t="n">
         <v>7</v>
       </c>
+      <c r="R338" t="n">
+        <v>0.008368775295968314</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U338" t="inlineStr">
         <is>
           <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
-      <c r="V338" t="inlineStr">
-        <is>
-          <t>scharlach</t>
-        </is>
-      </c>
-      <c r="W338" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X338" t="inlineStr">
-        <is>
-          <t>Scharlach</t>
-        </is>
-      </c>
-      <c r="Y338" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
-      </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD338" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE338" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF338" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG338" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ338" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL338" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM338" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN338" t="b">
-        <v>1</v>
       </c>
       <c r="AO338" t="inlineStr">
         <is>
@@ -62545,6 +62731,240 @@
         </is>
       </c>
       <c r="BC338" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>7</v>
+      </c>
+      <c r="O339" t="n">
+        <v>7</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>scharlach</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>Scharlach</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL339" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM339" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN339" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO339" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP339" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS339" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AT339" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV339" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA339" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB339" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC339" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -62666,7 +63086,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -62676,7 +63096,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11">
@@ -62728,7 +63148,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31631</v>
+        <v>31714</v>
       </c>
     </row>
     <row r="16">
